--- a/data/gravel/Standert Erdgeschoss 2025.xlsx
+++ b/data/gravel/Standert Erdgeschoss 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10905"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C409DFB4-190A-624E-8AEE-C2E0D7A006F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E495254-34E6-7642-A147-9472EFEAAFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31220" yWindow="-27040" windowWidth="28220" windowHeight="23740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9040" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="99">
   <si>
     <t>brand</t>
   </si>
@@ -327,6 +327,9 @@
   </si>
   <si>
     <t>steel</t>
+  </si>
+  <si>
+    <t>https://standert.de/cdn/shop/files/Standert_Bikes_Demo_Erdgeschoss_PangPink_50_5_a5074e23-8fb1-4142-b2db-fee519000367_1700x.webp?v=1752057318</t>
   </si>
 </sst>
 </file>
@@ -726,6 +729,11 @@
         <v>91</v>
       </c>
     </row>
+    <row r="6" spans="1:9">
+      <c r="B6" t="s">
+        <v>98</v>
+      </c>
+    </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
         <v>5</v>

--- a/data/gravel/Standert Erdgeschoss 2025.xlsx
+++ b/data/gravel/Standert Erdgeschoss 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E495254-34E6-7642-A147-9472EFEAAFD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5595BB-5FED-2A4F-968E-C66BE4D569DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9040" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
   <si>
     <t>brand</t>
   </si>
@@ -330,6 +330,12 @@
   </si>
   <si>
     <t>https://standert.de/cdn/shop/files/Standert_Bikes_Demo_Erdgeschoss_PangPink_50_5_a5074e23-8fb1-4142-b2db-fee519000367_1700x.webp?v=1752057318</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Berlin, Germany</t>
   </si>
 </sst>
 </file>
@@ -683,7 +689,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O73"/>
+  <dimension ref="A1:O74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1533,6 +1539,14 @@
         <v>76</v>
       </c>
     </row>
+    <row r="74" spans="1:2">
+      <c r="A74" t="s">
+        <v>99</v>
+      </c>
+      <c r="B74" t="s">
+        <v>100</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Standert Erdgeschoss 2025.xlsx
+++ b/data/gravel/Standert Erdgeschoss 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11012"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E5595BB-5FED-2A4F-968E-C66BE4D569DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4A12DC-845F-CF4D-A93A-C606E5F04C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="108" uniqueCount="107">
   <si>
     <t>brand</t>
   </si>
@@ -336,6 +336,24 @@
   </si>
   <si>
     <t>Berlin, Germany</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -689,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1386,164 +1404,194 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>77</v>
+        <v>101</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" t="s">
-        <v>43</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" t="s">
-        <v>44</v>
-      </c>
-      <c r="B52">
-        <v>27.2</v>
+        <v>103</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>67</v>
+        <v>104</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" t="s">
-        <v>46</v>
+        <v>105</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" t="s">
-        <v>47</v>
-      </c>
-      <c r="B55" s="1"/>
+        <v>106</v>
+      </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" t="s">
-        <v>50</v>
+        <v>44</v>
+      </c>
+      <c r="B58">
+        <v>27.2</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>90</v>
+        <v>67</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="1"/>
+        <v>46</v>
+      </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" t="s">
-        <v>53</v>
-      </c>
+        <v>47</v>
+      </c>
+      <c r="B61" s="1"/>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:2">
       <c r="A65" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1</v>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="66" spans="1:2">
       <c r="A66" t="s">
-        <v>58</v>
-      </c>
-      <c r="B66" s="1">
-        <v>3</v>
-      </c>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1"/>
     </row>
     <row r="67" spans="1:2">
       <c r="A67" t="s">
-        <v>59</v>
-      </c>
-      <c r="B67" s="1"/>
+        <v>53</v>
+      </c>
     </row>
     <row r="68" spans="1:2">
       <c r="A68" t="s">
-        <v>60</v>
-      </c>
-      <c r="B68" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="69" spans="1:2">
       <c r="A69" t="s">
-        <v>61</v>
-      </c>
-      <c r="B69" s="1"/>
+        <v>55</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
+      </c>
     </row>
     <row r="70" spans="1:2">
       <c r="A70" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B70">
-        <v>2199</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2">
       <c r="A71" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2">
       <c r="A72" t="s">
-        <v>64</v>
+        <v>58</v>
+      </c>
+      <c r="B72" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:2">
       <c r="A73" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>76</v>
-      </c>
+        <v>59</v>
+      </c>
+      <c r="B73" s="1"/>
     </row>
     <row r="74" spans="1:2">
       <c r="A74" t="s">
+        <v>60</v>
+      </c>
+      <c r="B74" s="1"/>
+    </row>
+    <row r="75" spans="1:2">
+      <c r="A75" t="s">
+        <v>61</v>
+      </c>
+      <c r="B75" s="1"/>
+    </row>
+    <row r="76" spans="1:2">
+      <c r="A76" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76">
+        <v>2199</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2">
+      <c r="A77" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2">
+      <c r="A78" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2">
+      <c r="A79" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2">
+      <c r="A80" t="s">
         <v>99</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>100</v>
       </c>
     </row>

--- a/data/gravel/Standert Erdgeschoss 2025.xlsx
+++ b/data/gravel/Standert Erdgeschoss 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11109"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF4A12DC-845F-CF4D-A93A-C606E5F04C2A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F64263F6-307D-F547-AB6E-414663CDC847}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -713,7 +713,7 @@
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:12">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -721,7 +721,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:12">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -729,7 +729,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:12">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -737,7 +737,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:12">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -745,7 +745,7 @@
         <v>45918</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:12">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -753,12 +753,12 @@
         <v>91</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:12">
       <c r="B6" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:12">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -766,21 +766,21 @@
         <v>93</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="21">
+    <row r="8" spans="1:12" ht="21">
       <c r="A8" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>94</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>96</v>
+      <c r="C8" s="1">
+        <v>48</v>
+      </c>
+      <c r="D8" s="2">
+        <v>50</v>
+      </c>
+      <c r="E8" s="2">
+        <v>52</v>
       </c>
       <c r="F8" s="2">
         <v>54</v>
@@ -794,8 +794,17 @@
       <c r="I8">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="21">
+      <c r="J8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="21">
       <c r="A9" t="s">
         <v>7</v>
       </c>
@@ -824,7 +833,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="10" spans="1:9" ht="21">
+    <row r="10" spans="1:12" ht="21">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -853,7 +862,7 @@
         <v>585</v>
       </c>
     </row>
-    <row r="11" spans="1:9" ht="21">
+    <row r="11" spans="1:12" ht="21">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -882,7 +891,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="12" spans="1:9" ht="21">
+    <row r="12" spans="1:12" ht="21">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -911,7 +920,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:9" ht="21">
+    <row r="13" spans="1:12" ht="21">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -940,7 +949,7 @@
         <v>72.5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" ht="21">
+    <row r="14" spans="1:12" ht="21">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -969,7 +978,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="15" spans="1:9" ht="21">
+    <row r="15" spans="1:12" ht="21">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -998,7 +1007,7 @@
         <v>398</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:12">
       <c r="A16" t="s">
         <v>15</v>
       </c>
